--- a/output/pdf_financials_xlsx/BAU.xlsx
+++ b/output/pdf_financials_xlsx/BAU.xlsx
@@ -6231,10 +6231,10 @@
         <v>0.34317</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.492932</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.47833</v>
       </c>
       <c r="G92" s="3" t="n">
         <v>0</v>
@@ -7914,34 +7914,34 @@
         </is>
       </c>
       <c r="G118" s="3" t="n">
-        <v>1.549669</v>
+        <v>1.54558</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0.7</v>
+        <v>0.310117</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0.015422</v>
+        <v>-0.491328</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.101202</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-0.04501</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0.03</v>
+        <v>-0.643904</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-1.91974</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-7.239491</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-5.489818</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-2.958292</v>
       </c>
       <c r="Q118" s="3" t="n">
         <v>0</v>
@@ -20525,7 +20525,11 @@
           <t>Reserves (Note 8(c))</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -27071,7 +27075,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>-</t>
@@ -30227,7 +30235,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BAU.xlsx
+++ b/output/pdf_financials_xlsx/BAU.xlsx
@@ -1159,10 +1159,10 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.000362</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.002818</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>0</v>
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>-0.010928</v>
       </c>
     </row>
     <row r="13">
@@ -2261,10 +2261,10 @@
         <v>-1.10889</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.669725</v>
+        <v>-0.670087</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.629972</v>
+        <v>-0.63279</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-0.660265</v>
@@ -2287,7 +2287,7 @@
         <v>-7.743745</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-4.289772</v>
+        <v>-4.278844</v>
       </c>
     </row>
     <row r="28">
@@ -2401,10 +2401,10 @@
         <v>-1.10889</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.669725</v>
+        <v>-0.670087</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.629972</v>
+        <v>-0.63279</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-0.660265</v>
@@ -2427,7 +2427,7 @@
         <v>-7.743745</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-4.289772</v>
+        <v>-4.278844</v>
       </c>
     </row>
     <row r="30">
@@ -2713,28 +2713,28 @@
         <v>0.001386</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.004134</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.043807</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.085105</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.131111</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.015137</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.094725</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>2.433209</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>1.055101</v>
@@ -2743,10 +2743,10 @@
         <v>3.487503</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.845871</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>2.199582</v>
       </c>
     </row>
     <row r="35">
@@ -2829,28 +2829,28 @@
         <v>0.001386</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.004134</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.043807</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.085105</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.131111</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.015137</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.094725</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>2.433209</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>1.055101</v>
@@ -2859,10 +2859,10 @@
         <v>3.487503</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.845871</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>2.199582</v>
       </c>
     </row>
     <row r="37">
@@ -3525,28 +3525,28 @@
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.007362</v>
+        <v>0.003228</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.144826</v>
+        <v>0.101019</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.114445</v>
+        <v>0.02934</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.16392</v>
+        <v>0.032809</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0.021006</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.031839</v>
+        <v>0.016702</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.350596</v>
+        <v>0.255871</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>2.728975</v>
+        <v>0.295766</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>0.524983</v>
@@ -3555,10 +3555,10 @@
         <v>0.185383</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>1.077845</v>
+        <v>0.231974</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>2.357725</v>
+        <v>0.158143</v>
       </c>
     </row>
     <row r="49">
@@ -9283,7 +9283,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -18723,7 +18723,11 @@
           <t>Reclamation deposits (note 5)</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -20129,7 +20133,11 @@
           <t>Reclamation Deposits (Note 6)</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -28277,7 +28285,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -30330,7 +30342,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -36912,7 +36928,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -50477,7 +50493,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -52471,7 +52487,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">

--- a/output/pdf_financials_xlsx/BAU.xlsx
+++ b/output/pdf_financials_xlsx/BAU.xlsx
@@ -7515,7 +7515,7 @@
         <v>0</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="K112" s="3" t="n">
         <v>0</v>
@@ -31748,7 +31748,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BAU.xlsx
+++ b/output/pdf_financials_xlsx/BAU.xlsx
@@ -564,20 +564,14 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
@@ -634,20 +628,14 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
@@ -704,20 +692,14 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
@@ -774,20 +756,14 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.135369</v>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
@@ -803,7 +779,7 @@
         <v>0.157368</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.162115</v>
+        <v>0.168115</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>0.219081</v>
@@ -826,16 +802,16 @@
         </is>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.173612</v>
+        <v>0.273612</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.272742</v>
+        <v>0.397921</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.264581</v>
+        <v>0.394581</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.260938</v>
+        <v>0.390938</v>
       </c>
     </row>
     <row r="8">
@@ -844,20 +820,14 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
@@ -914,20 +884,14 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0.014159</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0.06746000000000001</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0.03176</v>
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
@@ -984,20 +948,14 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0.023159</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0.10446</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0.167129</v>
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
@@ -1036,16 +994,16 @@
         </is>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.173612</v>
+        <v>0.273612</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.272742</v>
+        <v>0.397921</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.264581</v>
+        <v>0.394581</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.260938</v>
+        <v>0.390938</v>
       </c>
     </row>
     <row r="11">
@@ -1054,20 +1012,14 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>-0.042159</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>-0.132881</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>-0.519984</v>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
@@ -1106,16 +1058,16 @@
         </is>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.173612</v>
+        <v>-0.273612</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.272742</v>
+        <v>-0.397921</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-0.264581</v>
+        <v>-0.394581</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-0.260938</v>
+        <v>-0.390938</v>
       </c>
     </row>
     <row r="12">
@@ -1124,20 +1076,14 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0.018164</v>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
@@ -1194,20 +1140,14 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
@@ -1264,20 +1204,14 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E14" s="1" t="inlineStr">
         <is>
@@ -1334,20 +1268,14 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
@@ -1404,20 +1332,14 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-0.020706</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-0.132881</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-0.50182</v>
       </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
@@ -1448,7 +1370,7 @@
         <v>-0.660265</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>-1.388837</v>
+        <v>-1.064982</v>
       </c>
       <c r="N16" s="1" t="inlineStr">
         <is>
@@ -1456,16 +1378,16 @@
         </is>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-1.465712</v>
+        <v>-0.570638</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-2.531174</v>
+        <v>-2.278253</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>-7.743745</v>
+        <v>-7.349901</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>-4.289772</v>
+        <v>-4.25748</v>
       </c>
     </row>
     <row r="17">
@@ -1474,20 +1396,14 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
@@ -1518,7 +1434,7 @@
         <v>-0</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.323855</v>
       </c>
       <c r="N17" s="1" t="inlineStr">
         <is>
@@ -1526,16 +1442,16 @@
         </is>
       </c>
       <c r="O17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.895074</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.252921</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.393844</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.032292</v>
       </c>
     </row>
     <row r="18">
@@ -1728,20 +1644,14 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-0.020706</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-0.132881</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>-0.50182</v>
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
@@ -1798,20 +1708,14 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E21" s="1" t="inlineStr">
         <is>
@@ -1868,20 +1772,14 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E22" s="1" t="inlineStr">
         <is>
@@ -1938,20 +1836,14 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>-0.020706</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>-0.132881</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>-0.50182</v>
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
@@ -2011,15 +1903,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C24" s="3" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0.04</v>
       </c>
       <c r="E24" s="1" t="inlineStr">
         <is>
@@ -2081,15 +1969,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C25" s="3" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>0.04</v>
       </c>
       <c r="E25" s="1" t="inlineStr">
         <is>
@@ -2151,15 +2035,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C26" s="3" t="n">
+        <v>-3.322025</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>-12.5455</v>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
@@ -2226,20 +2106,14 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-0.020706</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-0.132881</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>-0.519984</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -2270,7 +2144,7 @@
         <v>-0.660265</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.388837</v>
+        <v>-1.064982</v>
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
@@ -2278,16 +2152,16 @@
         </is>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-1.465712</v>
+        <v>-0.570638</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-2.531174</v>
+        <v>-2.278253</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-7.743745</v>
+        <v>-7.349901</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-4.278844</v>
+        <v>-4.246552</v>
       </c>
     </row>
     <row r="28">
@@ -2296,20 +2170,14 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E28" s="1" t="inlineStr">
         <is>
@@ -2366,20 +2234,14 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-0.020706</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-0.132881</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>-0.519984</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -2410,7 +2272,7 @@
         <v>-0.660265</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.388837</v>
+        <v>-1.064982</v>
       </c>
       <c r="N29" s="1" t="inlineStr">
         <is>
@@ -2418,16 +2280,16 @@
         </is>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.465712</v>
+        <v>-0.570638</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-2.531174</v>
+        <v>-2.278253</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-7.743745</v>
+        <v>-7.349901</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-4.278844</v>
+        <v>-4.246552</v>
       </c>
     </row>
     <row r="30">
@@ -2528,20 +2390,14 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="E31" s="1" t="inlineStr">
         <is>
@@ -2572,7 +2428,7 @@
         <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-0</v>
+        <v>-30.40943415006075</v>
       </c>
       <c r="N31" s="1" t="inlineStr">
         <is>
@@ -2580,16 +2436,16 @@
         </is>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-0</v>
+        <v>-156.854958835549</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-0</v>
+        <v>-11.10153262170619</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-0</v>
+        <v>-5.358493944340203</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.7584768454578765</v>
       </c>
     </row>
     <row r="32">
@@ -6776,7 +6632,7 @@
         <v>0.015504</v>
       </c>
       <c r="M101" s="3" t="n">
-        <v>0</v>
+        <v>-0.087822</v>
       </c>
       <c r="N101" s="3" t="n">
         <v>0.200448</v>
@@ -7116,7 +6972,7 @@
         <v>-0.990363</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0.107925</v>
+        <v>0.020103</v>
       </c>
       <c r="N106" s="3" t="n">
         <v>0.191759</v>
@@ -7459,19 +7315,19 @@
         <v>0</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.252506</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-0.07982499999999999</v>
       </c>
       <c r="P111" s="3" t="n">
-        <v>0</v>
+        <v>-0.100912</v>
       </c>
       <c r="Q111" s="3" t="n">
-        <v>0</v>
+        <v>-0.100912</v>
       </c>
       <c r="R111" s="3" t="n">
-        <v>0</v>
+        <v>-0.641533</v>
       </c>
     </row>
     <row r="112">
@@ -9051,19 +8907,19 @@
         <v>0</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.252506</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-0.07982499999999999</v>
       </c>
       <c r="P134" s="3" t="n">
-        <v>0</v>
+        <v>-0.100912</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>0</v>
+        <v>-0.100912</v>
       </c>
       <c r="R134" s="3" t="n">
-        <v>0</v>
+        <v>-0.641533</v>
       </c>
     </row>
     <row r="135">
@@ -9123,19 +8979,19 @@
         <v>-1.01778</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-1.920622</v>
+        <v>-2.173128</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>-1.456455</v>
+        <v>-1.53628</v>
       </c>
       <c r="P135" s="3" t="n">
-        <v>-1.301601</v>
+        <v>-1.402513</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>-6.903189</v>
+        <v>-7.004101</v>
       </c>
       <c r="R135" s="3" t="n">
-        <v>-3.316448</v>
+        <v>-3.957981</v>
       </c>
     </row>
   </sheetData>
@@ -9149,7 +9005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U443"/>
+  <dimension ref="A1:U467"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -22416,7 +22272,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -22970,7 +22830,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
@@ -23176,7 +23040,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -25455,7 +25323,11 @@
           <t>Purchase of equipment -</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -25661,7 +25533,11 @@
           <t>Proceeds from private placement 3,542,500</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>
@@ -26885,7 +26761,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -28186,7 +28066,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -36081,7 +35965,11 @@
           <t>Directors fee 10</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E272" t="inlineStr">
         <is>
           <t>-</t>
@@ -37128,7 +37016,11 @@
           <t>Deferred income tax recovery 13, 16</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E283" t="inlineStr">
         <is>
           <t>-</t>
@@ -39536,7 +39428,11 @@
           <t>Directors fee 11 130,000</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E307" t="inlineStr">
         <is>
           <t>-</t>
@@ -40562,7 +40458,11 @@
           <t>Deferred income tax recovery 14, 17 393,844</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
@@ -42897,7 +42797,11 @@
           <t>Deferred income tax recovery 11, 13</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E340" t="inlineStr">
         <is>
           <t>-</t>
@@ -47826,7 +47730,11 @@
           <t>Deferred income tax recovery 15</t>
         </is>
       </c>
-      <c r="D389" t="inlineStr"/>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr">
         <is>
           <t>-</t>
@@ -50214,15 +50122,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F413" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G413" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F413" s="5" t="n">
+        <v>0.005721</v>
+      </c>
+      <c r="G413" s="5" t="n">
+        <v>0.028809</v>
       </c>
       <c r="H413" t="inlineStr">
         <is>
@@ -51104,10 +51008,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G422" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G422" s="5" t="n">
+        <v>0.044621</v>
       </c>
       <c r="H422" t="inlineStr">
         <is>
@@ -51195,20 +51097,14 @@
           <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
-      <c r="E423" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F423" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G423" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E423" s="5" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="F423" s="5" t="n">
+        <v>0.0227</v>
+      </c>
+      <c r="G423" s="5" t="n">
+        <v>0.0485</v>
       </c>
       <c r="H423" t="inlineStr">
         <is>
@@ -52085,7 +51981,11 @@
           <t>Directors' fees</t>
         </is>
       </c>
-      <c r="D432" t="inlineStr"/>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E432" t="inlineStr">
         <is>
           <t>-</t>
@@ -52191,20 +52091,14 @@
           <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
-      <c r="E433" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F433" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G433" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E433" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F433" s="5" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G433" s="5" t="n">
+        <v>0.04</v>
       </c>
       <c r="H433" t="inlineStr">
         <is>
@@ -53280,6 +53174,2410 @@
         </is>
       </c>
       <c r="U443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Management fees (Note</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr"/>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G444" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H444" s="5" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="I444" s="5" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Investor and shareholder relations                                 56,696            30,040</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Professional fees (Note</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr"/>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G445" s="5" t="n">
+        <v>0.054156</v>
+      </c>
+      <c r="H445" s="5" t="n">
+        <v>0.046065</v>
+      </c>
+      <c r="I445" s="5" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Insurance                                                      19,096            14,168</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Office (Note</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr"/>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G446" s="5" t="n">
+        <v>0.015917</v>
+      </c>
+      <c r="H446" s="5" t="n">
+        <v>0.015004</v>
+      </c>
+      <c r="I446" s="5" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Insurance                                                      19,096            14,168</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Directors’ fees (Note</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr"/>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G447" s="5" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="H447" s="5" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="I447" s="5" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Insurance                                                      19,096            14,168</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Rent (Note</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr"/>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G448" s="5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="H448" s="5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="I448" s="5" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Travel and entertainment                                        10,634            36,407</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Share-based payments (Note</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr"/>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G449" s="5" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I449" s="5" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Other Items</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Impairment of mineral property interests (Note</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr"/>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H450" s="5" t="n">
+        <v>1.244671</v>
+      </c>
+      <c r="I450" s="5" t="n">
+        <v>7e-06</v>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>Stock-based compensation $</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr"/>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G451" s="5" t="n">
+        <v>0.244862</v>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Regulatory and filing fees</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr"/>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G452" s="5" t="n">
+        <v>0.030684</v>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Directors’ fees</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E453" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F453" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G453" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>Investor relations</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G454" s="5" t="n">
+        <v>0.018748</v>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F455" s="5" t="n">
+        <v>0.05016</v>
+      </c>
+      <c r="G455" s="5" t="n">
+        <v>0.01653</v>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E456" s="5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="F456" s="5" t="n">
+        <v>0.0173</v>
+      </c>
+      <c r="G456" s="5" t="n">
+        <v>0.01523</v>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E457" s="5" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="F457" s="5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="G457" s="5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>Loss Before Other Item</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E458" s="5" t="n">
+        <v>-0.042159</v>
+      </c>
+      <c r="F458" s="5" t="n">
+        <v>-0.132881</v>
+      </c>
+      <c r="G458" s="5" t="n">
+        <v>-0.519984</v>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Other Item</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G459" s="5" t="n">
+        <v>0.018164</v>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Other Item</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Net Loss and Comprehensive Loss for Year</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E460" s="5" t="n">
+        <v>-0.020706</v>
+      </c>
+      <c r="F460" s="5" t="n">
+        <v>-0.132881</v>
+      </c>
+      <c r="G460" s="5" t="n">
+        <v>-0.50182</v>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Other Item</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Deficit, Beginning of Year</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr"/>
+      <c r="E461" s="5" t="n">
+        <v>-0.011055</v>
+      </c>
+      <c r="F461" s="5" t="n">
+        <v>-0.031761</v>
+      </c>
+      <c r="G461" s="5" t="n">
+        <v>-0.164642</v>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Other Item</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>Deficit, End of Year $</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr"/>
+      <c r="E462" s="5" t="n">
+        <v>-0.031761</v>
+      </c>
+      <c r="F462" s="5" t="n">
+        <v>-0.164642</v>
+      </c>
+      <c r="G462" s="5" t="n">
+        <v>-0.666462</v>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Other Item</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>Basic and Diluted Loss Per Share $</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F463" s="5" t="n">
+        <v>4e-08</v>
+      </c>
+      <c r="G463" s="5" t="n">
+        <v>4e-08</v>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Weighted Average Number of Common Shares</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>Outstanding</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr"/>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F464" s="5" t="n">
+        <v>3.319872</v>
+      </c>
+      <c r="G464" s="5" t="n">
+        <v>12.759127</v>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>Legal $</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E465" s="5" t="n">
+        <v>0.002159</v>
+      </c>
+      <c r="F465" s="5" t="n">
+        <v>0.05016</v>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E466" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F466" s="5" t="n">
+        <v>0.005721</v>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Other Item</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>Interest income, net</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr"/>
+      <c r="E467" s="5" t="n">
+        <v>0.021453</v>
+      </c>
+      <c r="F467" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U467" t="inlineStr">
         <is>
           <t>-</t>
         </is>
